--- a/output/yearly_benthic_cover_iteration_53_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_53_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.66001868390232</v>
+        <v>45.27183122499513</v>
       </c>
       <c r="M2" t="n">
-        <v>98.41921268302005</v>
+        <v>99.52891980526078</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.98403796977847</v>
+        <v>87.9129398010369</v>
       </c>
       <c r="C3" t="n">
-        <v>45.88990165288557</v>
+        <v>45.82650713566078</v>
       </c>
       <c r="D3" t="n">
-        <v>2.22864899189825</v>
+        <v>2.228514466587505</v>
       </c>
       <c r="E3" t="n">
-        <v>5.681902502768763</v>
+        <v>5.641931729849881</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428829972994169</v>
+        <v>0.7428381555291684</v>
       </c>
       <c r="G3" t="n">
-        <v>33.96010011512244</v>
+        <v>33.9388131917816</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17261787577317</v>
+        <v>34.17055515434174</v>
       </c>
       <c r="I3" t="n">
-        <v>6.554866753795076</v>
+        <v>6.547548630889711</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643018733121355</v>
+        <v>4.642738472057302</v>
       </c>
       <c r="K3" t="n">
-        <v>12.01596203022153</v>
+        <v>12.08706019896309</v>
       </c>
       <c r="L3" t="n">
-        <v>48.85884159699313</v>
+        <v>48.851386450364</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7647052801002</v>
+        <v>106.7649537849879</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.12333511025959</v>
+        <v>86.97201709902134</v>
       </c>
       <c r="C4" t="n">
-        <v>42.6632299078193</v>
+        <v>42.52055659602279</v>
       </c>
       <c r="D4" t="n">
-        <v>2.187407842583947</v>
+        <v>2.182926412455901</v>
       </c>
       <c r="E4" t="n">
-        <v>6.489063689715689</v>
+        <v>6.437803862856455</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444388048623556</v>
+        <v>0.7443948380260641</v>
       </c>
       <c r="G4" t="n">
-        <v>33.33166846677052</v>
+        <v>33.24453703780242</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24418502366835</v>
+        <v>34.24216254919894</v>
       </c>
       <c r="I4" t="n">
-        <v>5.47382875226901</v>
+        <v>5.467724661018643</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652742530389722</v>
+        <v>4.6524677376629</v>
       </c>
       <c r="K4" t="n">
-        <v>12.87666488974041</v>
+        <v>13.02798290097868</v>
       </c>
       <c r="L4" t="n">
-        <v>44.27802557039043</v>
+        <v>44.26958415214047</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81792036795014</v>
+        <v>99.81812364914194</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.0673047819941</v>
+        <v>85.79008365693609</v>
       </c>
       <c r="C5" t="n">
-        <v>42.45680246903773</v>
+        <v>42.18713491197489</v>
       </c>
       <c r="D5" t="n">
-        <v>2.136193142952215</v>
+        <v>2.125060557217335</v>
       </c>
       <c r="E5" t="n">
-        <v>7.098731985905084</v>
+        <v>7.027901101736067</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457562951751388</v>
+        <v>0.7457150386876092</v>
       </c>
       <c r="G5" t="n">
-        <v>32.5512600968647</v>
+        <v>32.36327802846259</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30478957805637</v>
+        <v>34.30289177963002</v>
       </c>
       <c r="I5" t="n">
-        <v>4.569596838195971</v>
+        <v>4.56451815940493</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660976844844617</v>
+        <v>4.660718991797558</v>
       </c>
       <c r="K5" t="n">
-        <v>13.93269521800588</v>
+        <v>14.20991634306389</v>
       </c>
       <c r="L5" t="n">
-        <v>43.45845151428225</v>
+        <v>43.45106750437738</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84794920132587</v>
+        <v>99.84811875941615</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.7422883443283</v>
+        <v>84.35789925665108</v>
       </c>
       <c r="C6" t="n">
-        <v>41.84159131075852</v>
+        <v>41.46373118129146</v>
       </c>
       <c r="D6" t="n">
-        <v>2.071558592690133</v>
+        <v>2.054840891382058</v>
       </c>
       <c r="E6" t="n">
-        <v>7.519564772039519</v>
+        <v>7.430589049788809</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468750196287816</v>
+        <v>0.746837555439966</v>
       </c>
       <c r="G6" t="n">
-        <v>31.56636036353943</v>
+        <v>31.29387858910328</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35625090292394</v>
+        <v>34.35452755023844</v>
       </c>
       <c r="I6" t="n">
-        <v>3.81370982082661</v>
+        <v>3.809490899198752</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667968872679885</v>
+        <v>4.667734721499788</v>
       </c>
       <c r="K6" t="n">
-        <v>15.25771165567172</v>
+        <v>15.64210074334892</v>
       </c>
       <c r="L6" t="n">
-        <v>42.7737637880643</v>
+        <v>42.76737590426502</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87306675449453</v>
+        <v>99.87320782890541</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.36718024448251</v>
+        <v>82.71510557698062</v>
       </c>
       <c r="C7" t="n">
-        <v>41.05893256761133</v>
+        <v>40.41244836426573</v>
       </c>
       <c r="D7" t="n">
-        <v>2.004893638947556</v>
+        <v>1.974587796707532</v>
       </c>
       <c r="E7" t="n">
-        <v>7.807933051913831</v>
+        <v>7.670156461533002</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478252965540946</v>
+        <v>0.7477942244763947</v>
       </c>
       <c r="G7" t="n">
-        <v>30.5505213904674</v>
+        <v>30.07167661148191</v>
       </c>
       <c r="H7" t="n">
-        <v>34.39996364148834</v>
+        <v>34.39853432591416</v>
       </c>
       <c r="I7" t="n">
-        <v>3.182135121648201</v>
+        <v>3.178642253890161</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673908103463091</v>
+        <v>4.673713902977467</v>
       </c>
       <c r="K7" t="n">
-        <v>16.6328197555175</v>
+        <v>17.28489442301936</v>
       </c>
       <c r="L7" t="n">
-        <v>42.20231129295934</v>
+        <v>42.19683802107052</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89406361608815</v>
+        <v>99.89418080835561</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.34075218597475</v>
+        <v>87.50028022338816</v>
       </c>
       <c r="C8" t="n">
-        <v>43.39255082601439</v>
+        <v>42.74596619412225</v>
       </c>
       <c r="D8" t="n">
-        <v>2.009203462029979</v>
+        <v>1.978732775075171</v>
       </c>
       <c r="E8" t="n">
-        <v>9.665408216956932</v>
+        <v>9.516746609187017</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494328604976863</v>
+        <v>0.7493639652035824</v>
       </c>
       <c r="G8" t="n">
-        <v>31.06178515854683</v>
+        <v>30.59085352438309</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47391158289356</v>
+        <v>34.47074239936479</v>
       </c>
       <c r="I8" t="n">
-        <v>5.697055526939221</v>
+        <v>5.510316167652127</v>
       </c>
       <c r="J8" t="n">
-        <v>4.683955378110539</v>
+        <v>4.68352478252239</v>
       </c>
       <c r="K8" t="n">
-        <v>11.65924781402525</v>
+        <v>12.49971977661183</v>
       </c>
       <c r="L8" t="n">
-        <v>44.7587068562504</v>
+        <v>44.57102158409253</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81050549629003</v>
+        <v>99.81670755482662</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.45982487477151</v>
+        <v>85.24102861504521</v>
       </c>
       <c r="C9" t="n">
-        <v>42.39616009890308</v>
+        <v>41.34176695545762</v>
       </c>
       <c r="D9" t="n">
-        <v>1.92429591806573</v>
+        <v>1.87588016016108</v>
       </c>
       <c r="E9" t="n">
-        <v>10.04966341780666</v>
+        <v>9.788773752919914</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508070985507226</v>
+        <v>0.750711992509468</v>
       </c>
       <c r="G9" t="n">
-        <v>29.74913567391339</v>
+        <v>29.00077055963451</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53712653333324</v>
+        <v>34.53275165543552</v>
       </c>
       <c r="I9" t="n">
-        <v>4.756251867159754</v>
+        <v>4.600190541200543</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692544365942016</v>
+        <v>4.691949953184174</v>
       </c>
       <c r="K9" t="n">
-        <v>13.5401751252285</v>
+        <v>14.75897138495477</v>
       </c>
       <c r="L9" t="n">
-        <v>43.90541323345345</v>
+        <v>43.74619732159729</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84174845758503</v>
+        <v>99.84693566200968</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.39741550159781</v>
+        <v>82.80297673185757</v>
       </c>
       <c r="C10" t="n">
-        <v>41.07208327226834</v>
+        <v>39.61699993498183</v>
       </c>
       <c r="D10" t="n">
-        <v>1.832044208156439</v>
+        <v>1.766139316852617</v>
       </c>
       <c r="E10" t="n">
-        <v>10.22950378677949</v>
+        <v>9.856023676859094</v>
       </c>
       <c r="F10" t="n">
-        <v>0.751984276059927</v>
+        <v>0.7518722956098612</v>
       </c>
       <c r="G10" t="n">
-        <v>28.32294721273294</v>
+        <v>27.30419682033111</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59127669875664</v>
+        <v>34.58612559805361</v>
       </c>
       <c r="I10" t="n">
-        <v>3.969757593737836</v>
+        <v>3.839417176589642</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699901725374544</v>
+        <v>4.699201847561632</v>
       </c>
       <c r="K10" t="n">
-        <v>15.60258449840219</v>
+        <v>17.19702326814243</v>
       </c>
       <c r="L10" t="n">
-        <v>43.19321412190838</v>
+        <v>43.05819372628682</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86788189257891</v>
+        <v>99.87221692941108</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>82.1363357281645</v>
+        <v>80.28340353872869</v>
       </c>
       <c r="C11" t="n">
-        <v>39.42675493164796</v>
+        <v>37.69191130216124</v>
       </c>
       <c r="D11" t="n">
-        <v>1.731795234241936</v>
+        <v>1.654020262464188</v>
       </c>
       <c r="E11" t="n">
-        <v>10.22184447957731</v>
+        <v>9.764299724584092</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529951997427305</v>
+        <v>0.7528724301376855</v>
       </c>
       <c r="G11" t="n">
-        <v>26.77312304164031</v>
+        <v>25.57085636461522</v>
       </c>
       <c r="H11" t="n">
-        <v>34.6377791881656</v>
+        <v>34.63213178633352</v>
       </c>
       <c r="I11" t="n">
-        <v>3.312578586404543</v>
+        <v>3.203770282233443</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706219998392067</v>
+        <v>4.705452688360533</v>
       </c>
       <c r="K11" t="n">
-        <v>17.86366427183551</v>
+        <v>19.71659646127132</v>
       </c>
       <c r="L11" t="n">
-        <v>42.59930975224604</v>
+        <v>42.48484175943994</v>
       </c>
       <c r="M11" t="n">
-        <v>99.8897289557295</v>
+        <v>99.8933495228725</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.76230675876971</v>
+        <v>77.8007596179832</v>
       </c>
       <c r="C12" t="n">
-        <v>37.56580934503036</v>
+        <v>35.70437295581035</v>
       </c>
       <c r="D12" t="n">
-        <v>1.627510222117126</v>
+        <v>1.544772546827026</v>
       </c>
       <c r="E12" t="n">
-        <v>10.06691855975013</v>
+        <v>9.564847294149249</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538648797677528</v>
+        <v>0.7537346012813341</v>
       </c>
       <c r="G12" t="n">
-        <v>25.16090272493603</v>
+        <v>23.88190629059478</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67778446931663</v>
+        <v>34.67179165894135</v>
       </c>
       <c r="I12" t="n">
-        <v>2.76367040433359</v>
+        <v>2.672865968181128</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711655498548456</v>
+        <v>4.710841258008337</v>
       </c>
       <c r="K12" t="n">
-        <v>20.23769324123029</v>
+        <v>22.1992403820168</v>
       </c>
       <c r="L12" t="n">
-        <v>42.10448134189479</v>
+        <v>42.00739304322192</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90798392815543</v>
+        <v>99.91100638104908</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>77.25685423035574</v>
+        <v>75.32476496298105</v>
       </c>
       <c r="C13" t="n">
-        <v>35.48758696987005</v>
+        <v>33.64049746231984</v>
       </c>
       <c r="D13" t="n">
-        <v>1.518379664948001</v>
+        <v>1.436881002523337</v>
       </c>
       <c r="E13" t="n">
-        <v>9.776119485905442</v>
+        <v>9.268407355243038</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546147256353277</v>
+        <v>0.7544782770577724</v>
       </c>
       <c r="G13" t="n">
-        <v>23.47377148856287</v>
+        <v>22.21392238195999</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71227737922507</v>
+        <v>34.70600074465751</v>
       </c>
       <c r="I13" t="n">
-        <v>2.305349450858223</v>
+        <v>2.229585969928317</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716342035220799</v>
+        <v>4.715489231611076</v>
       </c>
       <c r="K13" t="n">
-        <v>22.74314576964427</v>
+        <v>24.67523503701896</v>
       </c>
       <c r="L13" t="n">
-        <v>41.69249863814308</v>
+        <v>41.6100212237673</v>
       </c>
       <c r="M13" t="n">
-        <v>99.9232313776574</v>
+        <v>99.92575372310608</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.94453731465582</v>
+        <v>82.82408829475305</v>
       </c>
       <c r="C14" t="n">
-        <v>39.50782473660964</v>
+        <v>38.32480432523765</v>
       </c>
       <c r="D14" t="n">
-        <v>1.520295984649459</v>
+        <v>1.438558306086947</v>
       </c>
       <c r="E14" t="n">
-        <v>12.04830432844479</v>
+        <v>11.84920496622789</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555671113258952</v>
+        <v>0.755358996547106</v>
       </c>
       <c r="G14" t="n">
-        <v>25.23351942813603</v>
+        <v>24.32641946382734</v>
       </c>
       <c r="H14" t="n">
-        <v>36.48620923521281</v>
+        <v>36.83308011101317</v>
       </c>
       <c r="I14" t="n">
-        <v>3.178346781099986</v>
+        <v>2.900472722631191</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722294445786845</v>
+        <v>4.720993728419411</v>
       </c>
       <c r="K14" t="n">
-        <v>16.05546268534417</v>
+        <v>17.17591170524697</v>
       </c>
       <c r="L14" t="n">
-        <v>44.3309012279472</v>
+        <v>44.4027142734094</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89418864990101</v>
+        <v>99.90343030389403</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>83.06402743367096</v>
+        <v>81.98716801183672</v>
       </c>
       <c r="C15" t="n">
-        <v>39.10090656840958</v>
+        <v>37.92193640010721</v>
       </c>
       <c r="D15" t="n">
-        <v>1.485294272197509</v>
+        <v>1.406380056549884</v>
       </c>
       <c r="E15" t="n">
-        <v>12.23054975480918</v>
+        <v>12.0009386817266</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7563710458706724</v>
+        <v>0.7561020170469233</v>
       </c>
       <c r="G15" t="n">
-        <v>24.67029543653396</v>
+        <v>23.79581814103637</v>
       </c>
       <c r="H15" t="n">
-        <v>36.54275739679358</v>
+        <v>36.88285332788786</v>
       </c>
       <c r="I15" t="n">
-        <v>2.651440490774365</v>
+        <v>2.419438181045812</v>
       </c>
       <c r="J15" t="n">
-        <v>4.727319036691703</v>
+        <v>4.725637606543268</v>
       </c>
       <c r="K15" t="n">
-        <v>16.93597256632905</v>
+        <v>18.01283198816329</v>
       </c>
       <c r="L15" t="n">
-        <v>43.87483345467525</v>
+        <v>43.98466292498975</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91171258941387</v>
+        <v>99.91943131326025</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.48127502576958</v>
+        <v>79.4124757525872</v>
       </c>
       <c r="C16" t="n">
-        <v>36.9280137252286</v>
+        <v>35.72057971781108</v>
       </c>
       <c r="D16" t="n">
-        <v>1.386627478960574</v>
+        <v>1.310158450341242</v>
       </c>
       <c r="E16" t="n">
-        <v>11.78667801823519</v>
+        <v>11.51617705641282</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7570638605012916</v>
+        <v>0.7567424466349191</v>
       </c>
       <c r="G16" t="n">
-        <v>23.03146939075027</v>
+        <v>22.16775762359966</v>
       </c>
       <c r="H16" t="n">
-        <v>36.57622953603779</v>
+        <v>36.91409364999829</v>
       </c>
       <c r="I16" t="n">
-        <v>2.211557613151393</v>
+        <v>2.017906234132029</v>
       </c>
       <c r="J16" t="n">
-        <v>4.731649128133073</v>
+        <v>4.729640291468241</v>
       </c>
       <c r="K16" t="n">
-        <v>19.51872497423043</v>
+        <v>20.58752424741281</v>
       </c>
       <c r="L16" t="n">
-        <v>43.47961017579726</v>
+        <v>43.62468941863597</v>
       </c>
       <c r="M16" t="n">
-        <v>99.92634887525628</v>
+        <v>99.93279338385985</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.13605005118576</v>
+        <v>81.23748582991976</v>
       </c>
       <c r="C17" t="n">
-        <v>38.11566502047113</v>
+        <v>37.03872826899844</v>
       </c>
       <c r="D17" t="n">
-        <v>1.387893660723462</v>
+        <v>1.31124077950533</v>
       </c>
       <c r="E17" t="n">
-        <v>12.56238461496531</v>
+        <v>12.33794579211735</v>
       </c>
       <c r="F17" t="n">
-        <v>0.757755164018677</v>
+        <v>0.7573675957682042</v>
       </c>
       <c r="G17" t="n">
-        <v>23.44243642969503</v>
+        <v>22.66277200050738</v>
       </c>
       <c r="H17" t="n">
-        <v>36.99956480548345</v>
+        <v>37.4212900569045</v>
       </c>
       <c r="I17" t="n">
-        <v>2.250045601183088</v>
+        <v>2.013322131565719</v>
       </c>
       <c r="J17" t="n">
-        <v>4.735969775116732</v>
+        <v>4.733547473551273</v>
       </c>
       <c r="K17" t="n">
-        <v>17.86394994881426</v>
+        <v>18.76251417008024</v>
       </c>
       <c r="L17" t="n">
-        <v>43.94545193490647</v>
+        <v>44.13170221799326</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92506690419185</v>
+        <v>99.93294465707194</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.62347296918394</v>
+        <v>78.71312777546699</v>
       </c>
       <c r="C18" t="n">
-        <v>35.95039912089832</v>
+        <v>34.82459618727406</v>
       </c>
       <c r="D18" t="n">
-        <v>1.29565216095971</v>
+        <v>1.220952586799895</v>
       </c>
       <c r="E18" t="n">
-        <v>12.04022147379939</v>
+        <v>11.76821793681303</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7583504390208021</v>
+        <v>0.7579060874413561</v>
       </c>
       <c r="G18" t="n">
-        <v>21.88441685255804</v>
+        <v>21.10228001642413</v>
       </c>
       <c r="H18" t="n">
-        <v>37.02863081131758</v>
+        <v>37.44789675780752</v>
       </c>
       <c r="I18" t="n">
-        <v>1.876510987648382</v>
+        <v>1.678961343672578</v>
       </c>
       <c r="J18" t="n">
-        <v>4.739690243880013</v>
+        <v>4.736913046508473</v>
       </c>
       <c r="K18" t="n">
-        <v>20.37652703081608</v>
+        <v>21.28687222453302</v>
       </c>
       <c r="L18" t="n">
-        <v>43.61057258158608</v>
+        <v>43.83260597342721</v>
       </c>
       <c r="M18" t="n">
-        <v>99.93749873330049</v>
+        <v>99.9440743852343</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.59954938356266</v>
+        <v>77.74243455037001</v>
       </c>
       <c r="C19" t="n">
-        <v>35.21534386677897</v>
+        <v>34.10350844052849</v>
       </c>
       <c r="D19" t="n">
-        <v>1.258819805676336</v>
+        <v>1.186557033415885</v>
       </c>
       <c r="E19" t="n">
-        <v>11.95874566889926</v>
+        <v>11.67137100744962</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7588536922917499</v>
+        <v>0.7583636566860131</v>
       </c>
       <c r="G19" t="n">
-        <v>21.26229415560995</v>
+        <v>20.50780599124381</v>
       </c>
       <c r="H19" t="n">
-        <v>37.05320359273323</v>
+        <v>37.47050510746639</v>
       </c>
       <c r="I19" t="n">
-        <v>1.564796891528702</v>
+        <v>1.408058899820689</v>
       </c>
       <c r="J19" t="n">
-        <v>4.742835576823437</v>
+        <v>4.739772854287579</v>
       </c>
       <c r="K19" t="n">
-        <v>21.40045061643733</v>
+        <v>22.25756544963001</v>
       </c>
       <c r="L19" t="n">
-        <v>43.33208021157125</v>
+        <v>43.59201913224391</v>
       </c>
       <c r="M19" t="n">
-        <v>99.94787469478754</v>
+        <v>99.9530930224024</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.98558721614327</v>
+        <v>75.03311522843711</v>
       </c>
       <c r="C20" t="n">
-        <v>32.84208405665913</v>
+        <v>31.61034210294866</v>
       </c>
       <c r="D20" t="n">
-        <v>1.164052951052195</v>
+        <v>1.09077642239066</v>
       </c>
       <c r="E20" t="n">
-        <v>11.27592104359765</v>
+        <v>10.9249066809235</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7592880332699994</v>
+        <v>0.7587591774612927</v>
       </c>
       <c r="G20" t="n">
-        <v>19.66161967453295</v>
+        <v>18.85238603812671</v>
       </c>
       <c r="H20" t="n">
-        <v>37.07441153421024</v>
+        <v>37.49004766214918</v>
       </c>
       <c r="I20" t="n">
-        <v>1.304743771542729</v>
+        <v>1.173994388252685</v>
       </c>
       <c r="J20" t="n">
-        <v>4.745550207937496</v>
+        <v>4.742244859133076</v>
       </c>
       <c r="K20" t="n">
-        <v>24.01441278385672</v>
+        <v>24.96688477156289</v>
       </c>
       <c r="L20" t="n">
-        <v>43.10003657916391</v>
+        <v>43.38366037827122</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95653341967977</v>
+        <v>99.96088725278277</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.12460287295424</v>
+        <v>81.31132307475616</v>
       </c>
       <c r="C21" t="n">
-        <v>36.58560727952154</v>
+        <v>35.55782369354754</v>
       </c>
       <c r="D21" t="n">
-        <v>1.164977083477243</v>
+        <v>1.091509179291012</v>
       </c>
       <c r="E21" t="n">
-        <v>13.3117093923173</v>
+        <v>13.03562121759052</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7598908260302962</v>
+        <v>0.7592688933036758</v>
       </c>
       <c r="G21" t="n">
-        <v>21.37807500176244</v>
+        <v>20.69531127892923</v>
       </c>
       <c r="H21" t="n">
-        <v>38.80469073908517</v>
+        <v>39.34549322781489</v>
       </c>
       <c r="I21" t="n">
-        <v>1.955942167592432</v>
+        <v>1.638688694678859</v>
       </c>
       <c r="J21" t="n">
-        <v>4.749317662689352</v>
+        <v>4.74543058314797</v>
       </c>
       <c r="K21" t="n">
-        <v>17.87539712704578</v>
+        <v>18.68867692524384</v>
       </c>
       <c r="L21" t="n">
-        <v>45.47384924035369</v>
+        <v>45.69891309445059</v>
       </c>
       <c r="M21" t="n">
-        <v>99.934853646921</v>
+        <v>99.94541371324198</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_53_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_53_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.27183122499513</v>
+        <v>45.31346218249503</v>
       </c>
       <c r="M2" t="n">
-        <v>99.52891980526078</v>
+        <v>99.57773339460289</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.9129398010369</v>
+        <v>88.06559175157025</v>
       </c>
       <c r="C3" t="n">
-        <v>45.82650713566078</v>
+        <v>45.9374769421026</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228514466587505</v>
+        <v>2.228822114744915</v>
       </c>
       <c r="E3" t="n">
-        <v>5.641931729849881</v>
+        <v>5.713495064656916</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428381555291684</v>
+        <v>0.7429407049149717</v>
       </c>
       <c r="G3" t="n">
-        <v>33.9388131917816</v>
+        <v>33.97576899240939</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17055515434174</v>
+        <v>34.17527242608869</v>
       </c>
       <c r="I3" t="n">
-        <v>6.547548630889711</v>
+        <v>6.585913043036784</v>
       </c>
       <c r="J3" t="n">
-        <v>4.642738472057302</v>
+        <v>4.643379405718572</v>
       </c>
       <c r="K3" t="n">
-        <v>12.08706019896309</v>
+        <v>11.93440824842975</v>
       </c>
       <c r="L3" t="n">
-        <v>48.851386450364</v>
+        <v>48.89172400916225</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7649537849879</v>
+        <v>106.7636091996946</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>86.97201709902134</v>
+        <v>87.16194664449637</v>
       </c>
       <c r="C4" t="n">
-        <v>42.52055659602279</v>
+        <v>42.67209191451852</v>
       </c>
       <c r="D4" t="n">
-        <v>2.182926412455901</v>
+        <v>2.185361296728213</v>
       </c>
       <c r="E4" t="n">
-        <v>6.437803862856455</v>
+        <v>6.51871906606733</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7443948380260641</v>
+        <v>0.7445033243145011</v>
       </c>
       <c r="G4" t="n">
-        <v>33.24453703780242</v>
+        <v>33.31325999118047</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24216254919894</v>
+        <v>34.24715291846704</v>
       </c>
       <c r="I4" t="n">
-        <v>5.467724661018643</v>
+        <v>5.499804270773181</v>
       </c>
       <c r="J4" t="n">
-        <v>4.6524677376629</v>
+        <v>4.653145776965631</v>
       </c>
       <c r="K4" t="n">
-        <v>13.02798290097868</v>
+        <v>12.83805335550365</v>
       </c>
       <c r="L4" t="n">
-        <v>44.26958415214047</v>
+        <v>44.30691270100458</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81812364914194</v>
+        <v>99.81705797102674</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.79008365693609</v>
+        <v>86.02062089685492</v>
       </c>
       <c r="C5" t="n">
-        <v>42.18713491197489</v>
+        <v>42.38437963492314</v>
       </c>
       <c r="D5" t="n">
-        <v>2.125060557217335</v>
+        <v>2.129782360179307</v>
       </c>
       <c r="E5" t="n">
-        <v>7.027901101736067</v>
+        <v>7.118153266575304</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457150386876092</v>
+        <v>0.7458279122428398</v>
       </c>
       <c r="G5" t="n">
-        <v>32.36327802846259</v>
+        <v>32.4660245404296</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30289177963002</v>
+        <v>34.30808396317063</v>
       </c>
       <c r="I5" t="n">
-        <v>4.56451815940493</v>
+        <v>4.591324402739497</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660718991797558</v>
+        <v>4.661424451517748</v>
       </c>
       <c r="K5" t="n">
-        <v>14.20991634306389</v>
+        <v>13.97937910314508</v>
       </c>
       <c r="L5" t="n">
-        <v>43.45106750437738</v>
+        <v>43.48346892107699</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84811875941615</v>
+        <v>99.8472276591452</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.35789925665108</v>
+        <v>84.66463156255949</v>
       </c>
       <c r="C6" t="n">
-        <v>41.46373118129146</v>
+        <v>41.74148268995652</v>
       </c>
       <c r="D6" t="n">
-        <v>2.054840891382058</v>
+        <v>2.063658496287482</v>
       </c>
       <c r="E6" t="n">
-        <v>7.430589049788809</v>
+        <v>7.535800240355308</v>
       </c>
       <c r="F6" t="n">
-        <v>0.746837555439966</v>
+        <v>0.7469531046486431</v>
       </c>
       <c r="G6" t="n">
-        <v>31.29387858910328</v>
+        <v>31.45804408761034</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35452755023844</v>
+        <v>34.35984281383758</v>
       </c>
       <c r="I6" t="n">
-        <v>3.809490899198752</v>
+        <v>3.831875915766104</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667734721499788</v>
+        <v>4.668456904054018</v>
       </c>
       <c r="K6" t="n">
-        <v>15.64210074334892</v>
+        <v>15.33536843744054</v>
       </c>
       <c r="L6" t="n">
-        <v>42.76737590426502</v>
+        <v>42.79561208363796</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87320782890541</v>
+        <v>99.87246321103501</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.71510557698062</v>
+        <v>83.11880653042611</v>
       </c>
       <c r="C7" t="n">
-        <v>40.41244836426573</v>
+        <v>40.79083588506927</v>
       </c>
       <c r="D7" t="n">
-        <v>1.974587796707532</v>
+        <v>1.988507709063341</v>
       </c>
       <c r="E7" t="n">
-        <v>7.670156461533002</v>
+        <v>7.794261747743873</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7477942244763947</v>
+        <v>0.747910870797745</v>
       </c>
       <c r="G7" t="n">
-        <v>30.07167661148191</v>
+        <v>30.31245881661291</v>
       </c>
       <c r="H7" t="n">
-        <v>34.39853432591416</v>
+        <v>34.40390005669627</v>
       </c>
       <c r="I7" t="n">
-        <v>3.178642253890161</v>
+        <v>3.197324387026073</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673713902977467</v>
+        <v>4.674442942485905</v>
       </c>
       <c r="K7" t="n">
-        <v>17.28489442301936</v>
+        <v>16.88119346957389</v>
       </c>
       <c r="L7" t="n">
-        <v>42.19683802107052</v>
+        <v>42.22152964769668</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89418080835561</v>
+        <v>99.89355900233984</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.50028022338816</v>
+        <v>87.9676055029621</v>
       </c>
       <c r="C8" t="n">
-        <v>42.74596619412225</v>
+        <v>43.06576588593202</v>
       </c>
       <c r="D8" t="n">
-        <v>1.978732775075171</v>
+        <v>1.992763252907091</v>
       </c>
       <c r="E8" t="n">
-        <v>9.516746609187017</v>
+        <v>9.609625470047288</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7493639652035824</v>
+        <v>0.749511451719504</v>
       </c>
       <c r="G8" t="n">
-        <v>30.59085352438309</v>
+        <v>30.80602942480924</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47074239936479</v>
+        <v>34.47752677909718</v>
       </c>
       <c r="I8" t="n">
-        <v>5.510316167652127</v>
+        <v>5.647702551134893</v>
       </c>
       <c r="J8" t="n">
-        <v>4.68352478252239</v>
+        <v>4.684446573246899</v>
       </c>
       <c r="K8" t="n">
-        <v>12.49971977661183</v>
+        <v>12.03239449703791</v>
       </c>
       <c r="L8" t="n">
-        <v>44.57102158409253</v>
+        <v>44.71398488742208</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81670755482662</v>
+        <v>99.81214527039201</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.24102861504521</v>
+        <v>85.98964365292214</v>
       </c>
       <c r="C9" t="n">
-        <v>41.34176695545762</v>
+        <v>41.96437088154522</v>
       </c>
       <c r="D9" t="n">
-        <v>1.87588016016108</v>
+        <v>1.903291603435067</v>
       </c>
       <c r="E9" t="n">
-        <v>9.788773752919914</v>
+        <v>9.964006604432575</v>
       </c>
       <c r="F9" t="n">
-        <v>0.750711992509468</v>
+        <v>0.7508813694747873</v>
       </c>
       <c r="G9" t="n">
-        <v>29.00077055963451</v>
+        <v>29.42289158226798</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53275165543552</v>
+        <v>34.54054299584022</v>
       </c>
       <c r="I9" t="n">
-        <v>4.600190541200543</v>
+        <v>4.715020938254091</v>
       </c>
       <c r="J9" t="n">
-        <v>4.691949953184174</v>
+        <v>4.69300855921742</v>
       </c>
       <c r="K9" t="n">
-        <v>14.75897138495477</v>
+        <v>14.01035634707787</v>
       </c>
       <c r="L9" t="n">
-        <v>43.74619732159729</v>
+        <v>43.86839214495649</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84693566200968</v>
+        <v>99.84311937357958</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>82.80297673185757</v>
+        <v>83.79546759782053</v>
       </c>
       <c r="C10" t="n">
-        <v>39.61699993498183</v>
+        <v>40.50175912371077</v>
       </c>
       <c r="D10" t="n">
-        <v>1.766139316852617</v>
+        <v>1.804971159590512</v>
       </c>
       <c r="E10" t="n">
-        <v>9.856023676859094</v>
+        <v>10.10517404961026</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7518722956098612</v>
+        <v>0.7520568386932868</v>
       </c>
       <c r="G10" t="n">
-        <v>27.30419682033111</v>
+        <v>27.90296066136351</v>
       </c>
       <c r="H10" t="n">
-        <v>34.58612559805361</v>
+        <v>34.59461457989119</v>
       </c>
       <c r="I10" t="n">
-        <v>3.839417176589642</v>
+        <v>3.935335066838733</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699201847561632</v>
+        <v>4.700355241833041</v>
       </c>
       <c r="K10" t="n">
-        <v>17.19702326814243</v>
+        <v>16.20453240217947</v>
       </c>
       <c r="L10" t="n">
-        <v>43.05819372628682</v>
+        <v>43.16273567026938</v>
       </c>
       <c r="M10" t="n">
-        <v>99.87221692941108</v>
+        <v>99.86902719615961</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.28340353872869</v>
+        <v>81.51768489746546</v>
       </c>
       <c r="C11" t="n">
-        <v>37.69191130216124</v>
+        <v>38.83395432374119</v>
       </c>
       <c r="D11" t="n">
-        <v>1.654020262464188</v>
+        <v>1.703990407031842</v>
       </c>
       <c r="E11" t="n">
-        <v>9.764299724584092</v>
+        <v>10.08713915286837</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7528724301376855</v>
+        <v>0.753066697878907</v>
       </c>
       <c r="G11" t="n">
-        <v>25.57085636461522</v>
+        <v>26.34190415847807</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63213178633352</v>
+        <v>34.64106810242973</v>
       </c>
       <c r="I11" t="n">
-        <v>3.203770282233443</v>
+        <v>3.283849517035366</v>
       </c>
       <c r="J11" t="n">
-        <v>4.705452688360533</v>
+        <v>4.706666861743168</v>
       </c>
       <c r="K11" t="n">
-        <v>19.71659646127132</v>
+        <v>18.48231510253457</v>
       </c>
       <c r="L11" t="n">
-        <v>42.48484175943994</v>
+        <v>42.57441571075651</v>
       </c>
       <c r="M11" t="n">
-        <v>99.8933495228725</v>
+        <v>99.89068513703226</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>77.8007596179832</v>
+        <v>79.09675882889883</v>
       </c>
       <c r="C12" t="n">
-        <v>35.70437295581035</v>
+        <v>36.92126455838994</v>
       </c>
       <c r="D12" t="n">
-        <v>1.544772546827026</v>
+        <v>1.597652810015721</v>
       </c>
       <c r="E12" t="n">
-        <v>9.564847294149249</v>
+        <v>9.9142675884403</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7537346012813341</v>
+        <v>0.7539361719575244</v>
       </c>
       <c r="G12" t="n">
-        <v>23.88190629059478</v>
+        <v>24.69803645976211</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67179165894135</v>
+        <v>34.68106391004613</v>
       </c>
       <c r="I12" t="n">
-        <v>2.672865968181128</v>
+        <v>2.739700813942512</v>
       </c>
       <c r="J12" t="n">
-        <v>4.710841258008337</v>
+        <v>4.712101074734527</v>
       </c>
       <c r="K12" t="n">
-        <v>22.1992403820168</v>
+        <v>20.90324117110119</v>
       </c>
       <c r="L12" t="n">
-        <v>42.00739304322192</v>
+        <v>42.08427622836903</v>
       </c>
       <c r="M12" t="n">
-        <v>99.91100638104908</v>
+        <v>99.90878195786016</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>75.32476496298105</v>
+        <v>76.69444610427398</v>
       </c>
       <c r="C13" t="n">
-        <v>33.64049746231984</v>
+        <v>34.94209430748728</v>
       </c>
       <c r="D13" t="n">
-        <v>1.436881002523337</v>
+        <v>1.493139782027161</v>
       </c>
       <c r="E13" t="n">
-        <v>9.268407355243038</v>
+        <v>9.646601785113416</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7544782770577724</v>
+        <v>0.7546850351086326</v>
       </c>
       <c r="G13" t="n">
-        <v>22.21392238195999</v>
+        <v>23.08237468418761</v>
       </c>
       <c r="H13" t="n">
-        <v>34.70600074465751</v>
+        <v>34.71551161499711</v>
       </c>
       <c r="I13" t="n">
-        <v>2.229585969928317</v>
+        <v>2.285351733411106</v>
       </c>
       <c r="J13" t="n">
-        <v>4.715489231611076</v>
+        <v>4.716781469428953</v>
       </c>
       <c r="K13" t="n">
-        <v>24.67523503701896</v>
+        <v>23.30555389572602</v>
       </c>
       <c r="L13" t="n">
-        <v>41.6100212237673</v>
+        <v>41.67624899639942</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92575372310608</v>
+        <v>99.92389719961271</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.82408829475305</v>
+        <v>83.51331445304248</v>
       </c>
       <c r="C14" t="n">
-        <v>38.32480432523765</v>
+        <v>39.23634372988037</v>
       </c>
       <c r="D14" t="n">
-        <v>1.438558306086947</v>
+        <v>1.494844884221626</v>
       </c>
       <c r="E14" t="n">
-        <v>11.84920496622789</v>
+        <v>12.02824276701151</v>
       </c>
       <c r="F14" t="n">
-        <v>0.755358996547106</v>
+        <v>0.7555468533556462</v>
       </c>
       <c r="G14" t="n">
-        <v>24.32641946382734</v>
+        <v>25.00251546286013</v>
       </c>
       <c r="H14" t="n">
-        <v>36.83308011101317</v>
+        <v>36.64893694180638</v>
       </c>
       <c r="I14" t="n">
-        <v>2.900472722631191</v>
+        <v>2.861059710314379</v>
       </c>
       <c r="J14" t="n">
-        <v>4.720993728419411</v>
+        <v>4.722167833472788</v>
       </c>
       <c r="K14" t="n">
-        <v>17.17591170524697</v>
+        <v>16.48668554695753</v>
       </c>
       <c r="L14" t="n">
-        <v>44.4027142734094</v>
+        <v>44.1817108488809</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90343030389403</v>
+        <v>99.90474012571879</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>81.98716801183672</v>
+        <v>82.7492496672583</v>
       </c>
       <c r="C15" t="n">
-        <v>37.92193640010721</v>
+        <v>38.91445458587508</v>
       </c>
       <c r="D15" t="n">
-        <v>1.406380056549884</v>
+        <v>1.466606705171881</v>
       </c>
       <c r="E15" t="n">
-        <v>12.0009386817266</v>
+        <v>12.19877617353944</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7561020170469233</v>
+        <v>0.7562731918514626</v>
       </c>
       <c r="G15" t="n">
-        <v>23.79581814103637</v>
+        <v>24.53020859290562</v>
       </c>
       <c r="H15" t="n">
-        <v>36.88285332788786</v>
+        <v>36.68416908341793</v>
       </c>
       <c r="I15" t="n">
-        <v>2.419438181045812</v>
+        <v>2.386508471300337</v>
       </c>
       <c r="J15" t="n">
-        <v>4.725637606543268</v>
+        <v>4.726707449071641</v>
       </c>
       <c r="K15" t="n">
-        <v>18.01283198816329</v>
+        <v>17.2507503327417</v>
       </c>
       <c r="L15" t="n">
-        <v>43.98466292498975</v>
+        <v>43.75532120054115</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91943131326025</v>
+        <v>99.92052611915794</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.4124757525872</v>
+        <v>80.3584387530142</v>
       </c>
       <c r="C16" t="n">
-        <v>35.72057971781108</v>
+        <v>36.89251325912714</v>
       </c>
       <c r="D16" t="n">
-        <v>1.310158450341242</v>
+        <v>1.375941162511839</v>
       </c>
       <c r="E16" t="n">
-        <v>11.51617705641282</v>
+        <v>11.77638170200309</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7567424466349191</v>
+        <v>0.7568975964821887</v>
       </c>
       <c r="G16" t="n">
-        <v>22.16775762359966</v>
+        <v>23.01375250021431</v>
       </c>
       <c r="H16" t="n">
-        <v>36.91409364999829</v>
+        <v>36.71445676953034</v>
       </c>
       <c r="I16" t="n">
-        <v>2.017906234132029</v>
+        <v>1.99039904425876</v>
       </c>
       <c r="J16" t="n">
-        <v>4.729640291468241</v>
+        <v>4.730609978013679</v>
       </c>
       <c r="K16" t="n">
-        <v>20.58752424741281</v>
+        <v>19.64156124698579</v>
       </c>
       <c r="L16" t="n">
-        <v>43.62468941863597</v>
+        <v>43.39963359190651</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93279338385985</v>
+        <v>99.93370809801945</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.23748582991976</v>
+        <v>82.08239753914864</v>
       </c>
       <c r="C17" t="n">
-        <v>37.03872826899844</v>
+        <v>38.15519093269113</v>
       </c>
       <c r="D17" t="n">
-        <v>1.31124077950533</v>
+        <v>1.377039587381206</v>
       </c>
       <c r="E17" t="n">
-        <v>12.33794579211735</v>
+        <v>12.56620130376525</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7573675957682042</v>
+        <v>0.7575018339061365</v>
       </c>
       <c r="G17" t="n">
-        <v>22.66277200050738</v>
+        <v>23.48490780268356</v>
       </c>
       <c r="H17" t="n">
-        <v>37.4212900569045</v>
+        <v>37.1965494541401</v>
       </c>
       <c r="I17" t="n">
-        <v>2.013322131565719</v>
+        <v>1.965811095359042</v>
       </c>
       <c r="J17" t="n">
-        <v>4.733547473551273</v>
+        <v>4.734386461913353</v>
       </c>
       <c r="K17" t="n">
-        <v>18.76251417008024</v>
+        <v>17.91760246085135</v>
       </c>
       <c r="L17" t="n">
-        <v>44.13170221799326</v>
+        <v>43.86173183897774</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93294465707194</v>
+        <v>99.93452523252023</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>78.71312777546699</v>
+        <v>79.7720506667446</v>
       </c>
       <c r="C18" t="n">
-        <v>34.82459618727406</v>
+        <v>36.148332974132</v>
       </c>
       <c r="D18" t="n">
-        <v>1.220952586799895</v>
+        <v>1.292923382708742</v>
       </c>
       <c r="E18" t="n">
-        <v>11.76821793681303</v>
+        <v>12.07181359815525</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7579060874413561</v>
+        <v>0.7580207170946585</v>
       </c>
       <c r="G18" t="n">
-        <v>21.10228001642413</v>
+        <v>22.05033661856727</v>
       </c>
       <c r="H18" t="n">
-        <v>37.44789675780752</v>
+        <v>37.22202881711834</v>
       </c>
       <c r="I18" t="n">
-        <v>1.678961343672578</v>
+        <v>1.639298051258735</v>
       </c>
       <c r="J18" t="n">
-        <v>4.736913046508473</v>
+        <v>4.737629481841616</v>
       </c>
       <c r="K18" t="n">
-        <v>21.28687222453302</v>
+        <v>20.22794933325537</v>
       </c>
       <c r="L18" t="n">
-        <v>43.83260597342721</v>
+        <v>43.56911182885265</v>
       </c>
       <c r="M18" t="n">
-        <v>99.9440743852343</v>
+        <v>99.94539413624003</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>77.74243455037001</v>
+        <v>78.8417563596774</v>
       </c>
       <c r="C19" t="n">
-        <v>34.10350844052849</v>
+        <v>35.47048029435574</v>
       </c>
       <c r="D19" t="n">
-        <v>1.186557033415885</v>
+        <v>1.25968801289232</v>
       </c>
       <c r="E19" t="n">
-        <v>11.67137100744962</v>
+        <v>11.98931226096796</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7583636566860131</v>
+        <v>0.7584587745856474</v>
       </c>
       <c r="G19" t="n">
-        <v>20.50780599124381</v>
+        <v>21.48351951099875</v>
       </c>
       <c r="H19" t="n">
-        <v>37.47050510746639</v>
+        <v>37.24353929590266</v>
       </c>
       <c r="I19" t="n">
-        <v>1.408058899820689</v>
+        <v>1.366871163169758</v>
       </c>
       <c r="J19" t="n">
-        <v>4.739772854287579</v>
+        <v>4.740367341160296</v>
       </c>
       <c r="K19" t="n">
-        <v>22.25756544963001</v>
+        <v>21.1582436403226</v>
       </c>
       <c r="L19" t="n">
-        <v>43.59201913224391</v>
+        <v>43.32574000834224</v>
       </c>
       <c r="M19" t="n">
-        <v>99.9530930224024</v>
+        <v>99.95446394302058</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.03311522843711</v>
+        <v>76.42642138778122</v>
       </c>
       <c r="C20" t="n">
-        <v>31.61034210294866</v>
+        <v>33.26548680465542</v>
       </c>
       <c r="D20" t="n">
-        <v>1.09077642239066</v>
+        <v>1.172670601995468</v>
       </c>
       <c r="E20" t="n">
-        <v>10.9249066809235</v>
+        <v>11.35104563237568</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7587591774612927</v>
+        <v>0.758835764166238</v>
       </c>
       <c r="G20" t="n">
-        <v>18.85238603812671</v>
+        <v>19.99946931311939</v>
       </c>
       <c r="H20" t="n">
-        <v>37.49004766214918</v>
+        <v>37.26205108155185</v>
       </c>
       <c r="I20" t="n">
-        <v>1.173994388252685</v>
+        <v>1.139625468533613</v>
       </c>
       <c r="J20" t="n">
-        <v>4.742244859133076</v>
+        <v>4.742723526038987</v>
       </c>
       <c r="K20" t="n">
-        <v>24.96688477156289</v>
+        <v>23.57357861221877</v>
       </c>
       <c r="L20" t="n">
-        <v>43.38366037827122</v>
+        <v>43.12296593970442</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96088725278277</v>
+        <v>99.96203135657862</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.31132307475616</v>
+        <v>82.24692863690338</v>
       </c>
       <c r="C21" t="n">
-        <v>35.55782369354754</v>
+        <v>36.91429105470144</v>
       </c>
       <c r="D21" t="n">
-        <v>1.091509179291012</v>
+        <v>1.173427374514937</v>
       </c>
       <c r="E21" t="n">
-        <v>13.03562121759052</v>
+        <v>13.3083711320166</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7592688933036758</v>
+        <v>0.7593254720621584</v>
       </c>
       <c r="G21" t="n">
-        <v>20.69531127892923</v>
+        <v>21.69698938477509</v>
       </c>
       <c r="H21" t="n">
-        <v>39.34549322781489</v>
+        <v>38.97071140646809</v>
       </c>
       <c r="I21" t="n">
-        <v>1.638688694678859</v>
+        <v>1.592319666678012</v>
       </c>
       <c r="J21" t="n">
-        <v>4.74543058314797</v>
+        <v>4.745784200388489</v>
       </c>
       <c r="K21" t="n">
-        <v>18.68867692524384</v>
+        <v>17.75307136309662</v>
       </c>
       <c r="L21" t="n">
-        <v>45.69891309445059</v>
+        <v>45.27959449086548</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94541371324198</v>
+        <v>99.94695690866355</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_53_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_53_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.31346218249503</v>
+        <v>43.4569718348425</v>
       </c>
       <c r="M2" t="n">
-        <v>99.57773339460289</v>
+        <v>95.14827473603478</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.06559175157025</v>
+        <v>81.36751399957275</v>
       </c>
       <c r="C3" t="n">
-        <v>45.9374769421026</v>
+        <v>43.12306955512831</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228822114744915</v>
+        <v>2.173664710077362</v>
       </c>
       <c r="E3" t="n">
-        <v>5.713495064656916</v>
+        <v>4.150320679386897</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429407049149717</v>
+        <v>0.7375556794663832</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97576899240939</v>
+        <v>32.69554001408031</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17527242608869</v>
+        <v>33.92756125545363</v>
       </c>
       <c r="I3" t="n">
-        <v>6.585913043036784</v>
+        <v>3.073148664443263</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643379405718572</v>
+        <v>4.609722996664895</v>
       </c>
       <c r="K3" t="n">
-        <v>11.93440824842975</v>
+        <v>18.63248600042725</v>
       </c>
       <c r="L3" t="n">
-        <v>48.89172400916225</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7636091996946</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.16194664449637</v>
+        <v>88.39823747271473</v>
       </c>
       <c r="C4" t="n">
-        <v>42.67209191451852</v>
+        <v>42.70616682971202</v>
       </c>
       <c r="D4" t="n">
-        <v>2.185361296728213</v>
+        <v>2.17935480239173</v>
       </c>
       <c r="E4" t="n">
-        <v>6.51871906606733</v>
+        <v>6.518061830928429</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7445033243145011</v>
+        <v>0.7394864095756283</v>
       </c>
       <c r="G4" t="n">
-        <v>33.31325999118047</v>
+        <v>33.38105749194806</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24715291846704</v>
+        <v>34.0163748404789</v>
       </c>
       <c r="I4" t="n">
-        <v>5.499804270773181</v>
+        <v>6.942112037544307</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653145776965631</v>
+        <v>4.621790059847677</v>
       </c>
       <c r="K4" t="n">
-        <v>12.83805335550365</v>
+        <v>11.60176252728527</v>
       </c>
       <c r="L4" t="n">
-        <v>44.30691270100458</v>
+        <v>45.46127108200643</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81705797102674</v>
+        <v>99.76920043900373</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.02062089685492</v>
+        <v>87.21435016821299</v>
       </c>
       <c r="C5" t="n">
-        <v>42.38437963492314</v>
+        <v>42.59825545777881</v>
       </c>
       <c r="D5" t="n">
-        <v>2.129782360179307</v>
+        <v>2.122731660350764</v>
       </c>
       <c r="E5" t="n">
-        <v>7.118153266575304</v>
+        <v>7.315030923376246</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458279122428398</v>
+        <v>0.7411250840206985</v>
       </c>
       <c r="G5" t="n">
-        <v>32.4660245404296</v>
+        <v>32.51376394352268</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30808396317063</v>
+        <v>34.09175386495213</v>
       </c>
       <c r="I5" t="n">
-        <v>4.591324402739497</v>
+        <v>5.7979129168611</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661424451517748</v>
+        <v>4.632031775129366</v>
       </c>
       <c r="K5" t="n">
-        <v>13.97937910314508</v>
+        <v>12.78564983178701</v>
       </c>
       <c r="L5" t="n">
-        <v>43.48346892107699</v>
+        <v>44.42325826494683</v>
       </c>
       <c r="M5" t="n">
-        <v>99.8472276591452</v>
+        <v>99.80716355451266</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.66463156255949</v>
+        <v>85.74294957367984</v>
       </c>
       <c r="C6" t="n">
-        <v>41.74148268995652</v>
+        <v>42.02651669963462</v>
       </c>
       <c r="D6" t="n">
-        <v>2.063658496287482</v>
+        <v>2.052133911473506</v>
       </c>
       <c r="E6" t="n">
-        <v>7.535800240355308</v>
+        <v>7.878528914113354</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469531046486431</v>
+        <v>0.7425197775756256</v>
       </c>
       <c r="G6" t="n">
-        <v>31.45804408761034</v>
+        <v>31.43242211176238</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35984281383758</v>
+        <v>34.15590976847878</v>
       </c>
       <c r="I6" t="n">
-        <v>3.831875915766104</v>
+        <v>4.840686480428537</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668456904054018</v>
+        <v>4.640748609847661</v>
       </c>
       <c r="K6" t="n">
-        <v>15.33536843744054</v>
+        <v>14.25705042632015</v>
       </c>
       <c r="L6" t="n">
-        <v>42.79561208363796</v>
+        <v>43.55537973746574</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87246321103501</v>
+        <v>99.83894686342052</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.11880653042611</v>
+        <v>84.11701416180776</v>
       </c>
       <c r="C7" t="n">
-        <v>40.79083588506927</v>
+        <v>41.15198686977896</v>
       </c>
       <c r="D7" t="n">
-        <v>1.988507709063341</v>
+        <v>1.974623375242521</v>
       </c>
       <c r="E7" t="n">
-        <v>7.794261747743873</v>
+        <v>8.254345361548291</v>
       </c>
       <c r="F7" t="n">
-        <v>0.747910870797745</v>
+        <v>0.7437086176054917</v>
       </c>
       <c r="G7" t="n">
-        <v>30.31245881661291</v>
+        <v>30.24519749678977</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40390005669627</v>
+        <v>34.21059640985262</v>
       </c>
       <c r="I7" t="n">
-        <v>3.197324387026073</v>
+        <v>4.040364040734742</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674442942485905</v>
+        <v>4.648178860034323</v>
       </c>
       <c r="K7" t="n">
-        <v>16.88119346957389</v>
+        <v>15.88298583819224</v>
       </c>
       <c r="L7" t="n">
-        <v>42.22152964769668</v>
+        <v>42.83056377868355</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89355900233984</v>
+        <v>99.86553648665475</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.9676055029621</v>
+        <v>82.31495330027649</v>
       </c>
       <c r="C8" t="n">
-        <v>43.06576588593202</v>
+        <v>39.97697566197907</v>
       </c>
       <c r="D8" t="n">
-        <v>1.992763252907091</v>
+        <v>1.889281718057537</v>
       </c>
       <c r="E8" t="n">
-        <v>9.609625470047288</v>
+        <v>8.459526930349307</v>
       </c>
       <c r="F8" t="n">
-        <v>0.749511451719504</v>
+        <v>0.7447240116622189</v>
       </c>
       <c r="G8" t="n">
-        <v>30.80602942480924</v>
+        <v>28.93802403342178</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47752677909718</v>
+        <v>34.25730453646207</v>
       </c>
       <c r="I8" t="n">
-        <v>5.647702551134893</v>
+        <v>3.371566997434699</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684446573246899</v>
+        <v>4.654525072888869</v>
       </c>
       <c r="K8" t="n">
-        <v>12.03239449703791</v>
+        <v>17.68504669972352</v>
       </c>
       <c r="L8" t="n">
-        <v>44.71398488742208</v>
+        <v>42.22574530383256</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81214527039201</v>
+        <v>99.88776766553515</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.98964365292214</v>
+        <v>80.404567883292</v>
       </c>
       <c r="C9" t="n">
-        <v>41.96437088154522</v>
+        <v>38.58944447059453</v>
       </c>
       <c r="D9" t="n">
-        <v>1.903291603435067</v>
+        <v>1.799508410256998</v>
       </c>
       <c r="E9" t="n">
-        <v>9.964006604432575</v>
+        <v>8.526373479545095</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508813694747873</v>
+        <v>0.7455924721928409</v>
       </c>
       <c r="G9" t="n">
-        <v>29.42289158226798</v>
+        <v>27.56297122162472</v>
       </c>
       <c r="H9" t="n">
-        <v>34.54054299584022</v>
+        <v>34.29725372087069</v>
       </c>
       <c r="I9" t="n">
-        <v>4.715020938254091</v>
+        <v>2.812915627596404</v>
       </c>
       <c r="J9" t="n">
-        <v>4.69300855921742</v>
+        <v>4.659952951205256</v>
       </c>
       <c r="K9" t="n">
-        <v>14.01035634707787</v>
+        <v>19.59543211670799</v>
       </c>
       <c r="L9" t="n">
-        <v>43.86839214495649</v>
+        <v>41.72146877387986</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84311937357958</v>
+        <v>99.90634536118239</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.79546759782053</v>
+        <v>85.51566743567017</v>
       </c>
       <c r="C10" t="n">
-        <v>40.50175912371077</v>
+        <v>42.10941770051335</v>
       </c>
       <c r="D10" t="n">
-        <v>1.804971159590512</v>
+        <v>1.801512723163037</v>
       </c>
       <c r="E10" t="n">
-        <v>10.10517404961026</v>
+        <v>10.51341234549908</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520568386932868</v>
+        <v>0.746422921556758</v>
       </c>
       <c r="G10" t="n">
-        <v>27.90296066136351</v>
+        <v>29.09497165800523</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59461457989119</v>
+        <v>35.83675487758638</v>
       </c>
       <c r="I10" t="n">
-        <v>3.935335066838733</v>
+        <v>2.857449650129955</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700355241833041</v>
+        <v>4.665143259729739</v>
       </c>
       <c r="K10" t="n">
-        <v>16.20453240217947</v>
+        <v>14.48433256432983</v>
       </c>
       <c r="L10" t="n">
-        <v>43.16273567026938</v>
+        <v>43.31110738411702</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86902719615961</v>
+        <v>99.90485764896019</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.51768489746546</v>
+        <v>85.14688372804687</v>
       </c>
       <c r="C11" t="n">
-        <v>38.83395432374119</v>
+        <v>42.05471589395542</v>
       </c>
       <c r="D11" t="n">
-        <v>1.703990407031842</v>
+        <v>1.775830527665975</v>
       </c>
       <c r="E11" t="n">
-        <v>10.08713915286837</v>
+        <v>10.83197965117062</v>
       </c>
       <c r="F11" t="n">
-        <v>0.753066697878907</v>
+        <v>0.7471391650621887</v>
       </c>
       <c r="G11" t="n">
-        <v>26.34190415847807</v>
+        <v>28.74012090716688</v>
       </c>
       <c r="H11" t="n">
-        <v>34.64106810242973</v>
+        <v>35.93106710008616</v>
       </c>
       <c r="I11" t="n">
-        <v>3.283849517035366</v>
+        <v>2.451126595256385</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706666861743168</v>
+        <v>4.66961978163868</v>
       </c>
       <c r="K11" t="n">
-        <v>18.48231510253457</v>
+        <v>14.8531162719531</v>
       </c>
       <c r="L11" t="n">
-        <v>42.57441571075651</v>
+        <v>43.01054193984084</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89068513703226</v>
+        <v>99.91837410574936</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.09675882889883</v>
+        <v>83.10117676679964</v>
       </c>
       <c r="C12" t="n">
-        <v>36.92126455838994</v>
+        <v>40.38979753915957</v>
       </c>
       <c r="D12" t="n">
-        <v>1.597652810015721</v>
+        <v>1.689354666266881</v>
       </c>
       <c r="E12" t="n">
-        <v>9.9142675884403</v>
+        <v>10.64521886439934</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539361719575244</v>
+        <v>0.7477518166233094</v>
       </c>
       <c r="G12" t="n">
-        <v>24.69803645976211</v>
+        <v>27.34059168777233</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68106391004613</v>
+        <v>35.96053045227138</v>
       </c>
       <c r="I12" t="n">
-        <v>2.739700813942512</v>
+        <v>2.04428042557073</v>
       </c>
       <c r="J12" t="n">
-        <v>4.712101074734527</v>
+        <v>4.673448853895684</v>
       </c>
       <c r="K12" t="n">
-        <v>20.90324117110119</v>
+        <v>16.89882323320035</v>
       </c>
       <c r="L12" t="n">
-        <v>42.08427622836903</v>
+        <v>42.64329237777183</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90878195786016</v>
+        <v>99.93191315013175</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.69444610427398</v>
+        <v>84.22594547660114</v>
       </c>
       <c r="C13" t="n">
-        <v>34.94209430748728</v>
+        <v>41.34414448520463</v>
       </c>
       <c r="D13" t="n">
-        <v>1.493139782027161</v>
+        <v>1.69061338483354</v>
       </c>
       <c r="E13" t="n">
-        <v>9.646601785113416</v>
+        <v>11.27099685406506</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546850351086326</v>
+        <v>0.7483089578285462</v>
       </c>
       <c r="G13" t="n">
-        <v>23.08237468418761</v>
+        <v>27.66503033097406</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71551161499711</v>
+        <v>36.29139171186207</v>
       </c>
       <c r="I13" t="n">
-        <v>2.285351733411106</v>
+        <v>1.882673250609447</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716781469428953</v>
+        <v>4.676930986428414</v>
       </c>
       <c r="K13" t="n">
-        <v>23.30555389572602</v>
+        <v>15.77405452339886</v>
       </c>
       <c r="L13" t="n">
-        <v>41.67624899639942</v>
+        <v>42.81909194016288</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92389719961271</v>
+        <v>99.93729094876637</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.51331445304248</v>
+        <v>82.0843021296949</v>
       </c>
       <c r="C14" t="n">
-        <v>39.23634372988037</v>
+        <v>39.49478857671293</v>
       </c>
       <c r="D14" t="n">
-        <v>1.494844884221626</v>
+        <v>1.602513256894303</v>
       </c>
       <c r="E14" t="n">
-        <v>12.02824276701151</v>
+        <v>10.94529920568044</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555468533556462</v>
+        <v>0.748786014600786</v>
       </c>
       <c r="G14" t="n">
-        <v>25.00251546286013</v>
+        <v>26.22336854510001</v>
       </c>
       <c r="H14" t="n">
-        <v>36.64893694180638</v>
+        <v>36.31452794992126</v>
       </c>
       <c r="I14" t="n">
-        <v>2.861059710314379</v>
+        <v>1.569894566243176</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722167833472788</v>
+        <v>4.679912591254912</v>
       </c>
       <c r="K14" t="n">
-        <v>16.48668554695753</v>
+        <v>17.91569787030511</v>
       </c>
       <c r="L14" t="n">
-        <v>44.1817108488809</v>
+        <v>42.53721707379836</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90474012571879</v>
+        <v>99.9477035208164</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.7492496672583</v>
+        <v>81.05045307478372</v>
       </c>
       <c r="C15" t="n">
-        <v>38.91445458587508</v>
+        <v>38.66990461111062</v>
       </c>
       <c r="D15" t="n">
-        <v>1.466606705171881</v>
+        <v>1.558660554668675</v>
       </c>
       <c r="E15" t="n">
-        <v>12.19877617353944</v>
+        <v>10.87315851841373</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562731918514626</v>
+        <v>0.7491980146898518</v>
       </c>
       <c r="G15" t="n">
-        <v>24.53020859290562</v>
+        <v>25.51016463566856</v>
       </c>
       <c r="H15" t="n">
-        <v>36.68416908341793</v>
+        <v>36.33890645275076</v>
       </c>
       <c r="I15" t="n">
-        <v>2.386508471300337</v>
+        <v>1.33787730678056</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726707449071641</v>
+        <v>4.682487591811574</v>
       </c>
       <c r="K15" t="n">
-        <v>17.2507503327417</v>
+        <v>18.9495469252163</v>
       </c>
       <c r="L15" t="n">
-        <v>43.75532120054115</v>
+        <v>42.3359770776965</v>
       </c>
       <c r="M15" t="n">
-        <v>99.92052611915794</v>
+        <v>99.9554286140234</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.3584387530142</v>
+        <v>78.49451219668532</v>
       </c>
       <c r="C16" t="n">
-        <v>36.89251325912714</v>
+        <v>36.32105713795083</v>
       </c>
       <c r="D16" t="n">
-        <v>1.375941162511839</v>
+        <v>1.454350806082895</v>
       </c>
       <c r="E16" t="n">
-        <v>11.77638170200309</v>
+        <v>10.3314018701455</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7568975964821887</v>
+        <v>0.7495528908089238</v>
       </c>
       <c r="G16" t="n">
-        <v>23.01375250021431</v>
+        <v>23.80295593550737</v>
       </c>
       <c r="H16" t="n">
-        <v>36.71445676953034</v>
+        <v>36.35611927211282</v>
       </c>
       <c r="I16" t="n">
-        <v>1.99039904425876</v>
+        <v>1.115425854472046</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730609978013679</v>
+        <v>4.684705567555774</v>
       </c>
       <c r="K16" t="n">
-        <v>19.64156124698579</v>
+        <v>21.50548780331469</v>
       </c>
       <c r="L16" t="n">
-        <v>43.39963359190651</v>
+        <v>42.1362918002128</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93370809801945</v>
+        <v>99.96283674147831</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.08239753914864</v>
+        <v>83.53377407519899</v>
       </c>
       <c r="C17" t="n">
-        <v>38.15519093269113</v>
+        <v>39.66930275316609</v>
       </c>
       <c r="D17" t="n">
-        <v>1.377039587381206</v>
+        <v>1.455058636611491</v>
       </c>
       <c r="E17" t="n">
-        <v>12.56620130376525</v>
+        <v>12.10440081223222</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7575018339061365</v>
+        <v>0.7499176971656109</v>
       </c>
       <c r="G17" t="n">
-        <v>23.48490780268356</v>
+        <v>25.37923260201617</v>
       </c>
       <c r="H17" t="n">
-        <v>37.1965494541401</v>
+        <v>37.93850554587933</v>
       </c>
       <c r="I17" t="n">
-        <v>1.965811095359042</v>
+        <v>1.219673174009094</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734386461913353</v>
+        <v>4.686985607285068</v>
       </c>
       <c r="K17" t="n">
-        <v>17.91760246085135</v>
+        <v>16.46622592480103</v>
       </c>
       <c r="L17" t="n">
-        <v>43.86173183897774</v>
+        <v>43.82383532704855</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93452523252023</v>
+        <v>99.95936400501566</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.7720506667446</v>
+        <v>85.14318253920189</v>
       </c>
       <c r="C18" t="n">
-        <v>36.148332974132</v>
+        <v>40.43254528249665</v>
       </c>
       <c r="D18" t="n">
-        <v>1.292923382708742</v>
+        <v>1.456209035991796</v>
       </c>
       <c r="E18" t="n">
-        <v>12.07181359815525</v>
+        <v>12.72251319955602</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7580207170946585</v>
+        <v>0.7505105975700288</v>
       </c>
       <c r="G18" t="n">
-        <v>22.05033661856727</v>
+        <v>25.53527925392315</v>
       </c>
       <c r="H18" t="n">
-        <v>37.22202881711834</v>
+        <v>37.96850051114843</v>
       </c>
       <c r="I18" t="n">
-        <v>1.639298051258735</v>
+        <v>2.019478706199776</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737629481841616</v>
+        <v>4.69069123481268</v>
       </c>
       <c r="K18" t="n">
-        <v>20.22794933325537</v>
+        <v>14.85681746079811</v>
       </c>
       <c r="L18" t="n">
-        <v>43.56911182885265</v>
+        <v>44.64337447917168</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94539413624003</v>
+        <v>99.93273722246644</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.8417563596774</v>
+        <v>82.23845615421574</v>
       </c>
       <c r="C19" t="n">
-        <v>35.47048029435574</v>
+        <v>37.84026885569369</v>
       </c>
       <c r="D19" t="n">
-        <v>1.25968801289232</v>
+        <v>1.350621570348283</v>
       </c>
       <c r="E19" t="n">
-        <v>11.98931226096796</v>
+        <v>12.08069804657086</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7584587745856474</v>
+        <v>0.7510228865343915</v>
       </c>
       <c r="G19" t="n">
-        <v>21.48351951099875</v>
+        <v>23.68375563727098</v>
       </c>
       <c r="H19" t="n">
-        <v>37.24353929590266</v>
+        <v>37.99441732547222</v>
       </c>
       <c r="I19" t="n">
-        <v>1.366871163169758</v>
+        <v>1.684047647179044</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740367341160296</v>
+        <v>4.693893040839947</v>
       </c>
       <c r="K19" t="n">
-        <v>21.1582436403226</v>
+        <v>17.76154384578428</v>
       </c>
       <c r="L19" t="n">
-        <v>43.32574000834224</v>
+        <v>44.34209066779426</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95446394302058</v>
+        <v>99.94390336927222</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.42642138778122</v>
+        <v>79.20970558175205</v>
       </c>
       <c r="C20" t="n">
-        <v>33.26548680465542</v>
+        <v>35.0712430748135</v>
       </c>
       <c r="D20" t="n">
-        <v>1.172670601995468</v>
+        <v>1.241137994478826</v>
       </c>
       <c r="E20" t="n">
-        <v>11.35104563237568</v>
+        <v>11.33545078255433</v>
       </c>
       <c r="F20" t="n">
-        <v>0.758835764166238</v>
+        <v>0.7514666823521774</v>
       </c>
       <c r="G20" t="n">
-        <v>19.99946931311939</v>
+        <v>21.76391197853377</v>
       </c>
       <c r="H20" t="n">
-        <v>37.26205108155185</v>
+        <v>38.01686905605271</v>
       </c>
       <c r="I20" t="n">
-        <v>1.139625468533613</v>
+        <v>1.404202323079133</v>
       </c>
       <c r="J20" t="n">
-        <v>4.742723526038987</v>
+        <v>4.696666764701108</v>
       </c>
       <c r="K20" t="n">
-        <v>23.57357861221877</v>
+        <v>20.79029441824794</v>
       </c>
       <c r="L20" t="n">
-        <v>43.12296593970442</v>
+        <v>44.09168340562804</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96203135657862</v>
+        <v>99.95322089868948</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.24692863690338</v>
+        <v>76.22604668134447</v>
       </c>
       <c r="C21" t="n">
-        <v>36.91429105470144</v>
+        <v>32.30333663793915</v>
       </c>
       <c r="D21" t="n">
-        <v>1.173427374514937</v>
+        <v>1.133882499171904</v>
       </c>
       <c r="E21" t="n">
-        <v>13.3083711320166</v>
+        <v>10.55100241271149</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7593254720621584</v>
+        <v>0.7518514121370656</v>
       </c>
       <c r="G21" t="n">
-        <v>21.69698938477509</v>
+        <v>19.88313871282281</v>
       </c>
       <c r="H21" t="n">
-        <v>38.97071140646809</v>
+        <v>38.03633262269851</v>
       </c>
       <c r="I21" t="n">
-        <v>1.592319666678012</v>
+        <v>1.170767695946024</v>
       </c>
       <c r="J21" t="n">
-        <v>4.745784200388489</v>
+        <v>4.69907132585666</v>
       </c>
       <c r="K21" t="n">
-        <v>17.75307136309662</v>
+        <v>23.77395331865555</v>
       </c>
       <c r="L21" t="n">
-        <v>45.27959449086548</v>
+        <v>43.88370442331976</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94695690866355</v>
+        <v>99.96099437991447</v>
       </c>
     </row>
   </sheetData>
